--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487130_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487130_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8669</v>
+        <v>4.4461</v>
       </c>
       <c r="E2" t="n">
-        <v>5.461</v>
+        <v>5.2984</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4059</v>
+        <v>-0.8522999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>3.0982</v>
@@ -610,13 +610,13 @@
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2387</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2273</v>
+        <v>-0.3899</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4661</v>
+        <v>1.2079</v>
       </c>
       <c r="V2" t="n">
         <v>7.2853</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.755</v>
+        <v>3.1135</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0951</v>
+        <v>2.2127</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6599</v>
+        <v>0.9008</v>
       </c>
       <c r="G3" t="n">
         <v>3.0628</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7674</v>
+        <v>0.1259</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4707</v>
+        <v>-0.4118</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2967</v>
+        <v>0.5377</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6543</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. CARTÓN CHARFOLE</t>
+          <t>A. FRECHILLA GOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.7206</v>
+        <v>-1.575</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.883</v>
+        <v>-1.3429</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1623</v>
+        <v>-0.232</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7906</v>
+        <v>-2.9101</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1883</v>
+        <v>-0.0205</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6022</v>
+        <v>-2.8896</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0097</v>
+        <v>-0.9228</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0723</v>
+        <v>0.828</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.08210000000000001</v>
+        <v>-1.7507</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7808</v>
+        <v>-1.9873</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2607</v>
+        <v>-0.8484</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5202</v>
+        <v>-1.1389</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.193</v>
+        <v>1.3511</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7371</v>
+        <v>2.3161</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1785</v>
+        <v>-0.5896</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0569</v>
+        <v>-0.6831</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1216</v>
+        <v>0.0935</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.5737</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X4" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.6543</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FRECHILLA GOMEZ</t>
+          <t>R. CARTÓN CHARFOLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.969</v>
+        <v>-1.7018</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.2819</v>
+        <v>-1.8641</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6871</v>
+        <v>0.1623</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.9101</v>
+        <v>-1.7906</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0205</v>
+        <v>-0.1883</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.8896</v>
+        <v>-1.6022</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9228</v>
+        <v>-0.0097</v>
       </c>
       <c r="K5" t="n">
-        <v>0.828</v>
+        <v>0.0723</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.7507</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9873</v>
+        <v>-1.7808</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8484</v>
+        <v>-0.2607</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1389</v>
+        <v>-1.5202</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3511</v>
+        <v>-0.193</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3161</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9836</v>
+        <v>0.1973</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.622</v>
+        <v>0.0757</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3616</v>
+        <v>0.1216</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5737</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6543</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.9048</v>
+        <v>-4.1512</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.1278</v>
+        <v>-2.5081</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.777</v>
+        <v>-1.6431</v>
       </c>
       <c r="G6" t="n">
         <v>-4.128</v>
@@ -922,13 +922,13 @@
         <v>2.1231</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7219</v>
+        <v>-0.9684</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.4581</v>
+        <v>-0.8384</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2638</v>
+        <v>-0.1299</v>
       </c>
       <c r="V6" t="n">
         <v>1.7172</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.3426</v>
+        <v>-4.837</v>
       </c>
       <c r="E7" t="n">
-        <v>-5.7575</v>
+        <v>-5.5196</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4149</v>
+        <v>0.6826</v>
       </c>
       <c r="G7" t="n">
         <v>-3.0817</v>
@@ -1000,13 +1000,13 @@
         <v>1.3511</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.431</v>
+        <v>0.0747</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4785</v>
+        <v>-0.2406</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0476</v>
+        <v>0.3152</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2859</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.9515</v>
+        <v>-5.3715</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.9636</v>
+        <v>-3.5442</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9879</v>
+        <v>-1.8273</v>
       </c>
       <c r="G8" t="n">
         <v>-3.5973</v>
@@ -1078,13 +1078,13 @@
         <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.051</v>
+        <v>-0.471</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7733</v>
+        <v>-0.3539</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2776</v>
+        <v>-0.117</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8822</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-11.2666</v>
+        <v>-10.0769</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.457699999999999</v>
+        <v>-7.267799999999999</v>
       </c>
       <c r="F9" t="n">
         <v>-2.809</v>
@@ -1132,7 +1132,7 @@
         <v>3.0272</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0352999999999999</v>
+        <v>0.03530000000000079</v>
       </c>
       <c r="L9" t="n">
         <v>2.992</v>
@@ -1156,10 +1156,10 @@
         <v>11.5806</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.0029</v>
+        <v>-0.8131</v>
       </c>
       <c r="T9" t="n">
-        <v>-4.0316</v>
+        <v>-2.842</v>
       </c>
       <c r="U9" t="n">
         <v>2.029</v>
@@ -1171,7 +1171,7 @@
         <v>10.8827</v>
       </c>
       <c r="X9" t="n">
-        <v>-4.0445</v>
+        <v>-4.044499999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>8.933</v>
+        <v>9.3256</v>
       </c>
       <c r="E10" t="n">
-        <v>5.0563</v>
+        <v>5.557</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8767</v>
+        <v>3.7686</v>
       </c>
       <c r="G10" t="n">
         <v>4.3744</v>
@@ -1234,13 +1234,13 @@
         <v>3.0881</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2571</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.117</v>
+        <v>-0.6163</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3741</v>
+        <v>1.2661</v>
       </c>
       <c r="V10" t="n">
         <v>2.3714</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. MAESTRO STEELE</t>
+          <t>D. GARCIA CARRERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.1582</v>
+        <v>3.5953</v>
       </c>
       <c r="E11" t="n">
-        <v>5.178</v>
+        <v>0.0117</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0198</v>
+        <v>3.5836</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2698</v>
+        <v>1.4841</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3673</v>
+        <v>1.8961</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9025</v>
+        <v>-0.412</v>
       </c>
       <c r="J11" t="n">
-        <v>6.1107</v>
+        <v>1.3029</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8215</v>
+        <v>1.8163</v>
       </c>
       <c r="L11" t="n">
-        <v>4.2891</v>
+        <v>-0.5134</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8409</v>
+        <v>0.1812</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4542</v>
+        <v>0.0798</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3866</v>
+        <v>0.1014</v>
       </c>
       <c r="P11" t="n">
-        <v>0.386</v>
+        <v>1.9301</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.158</v>
+        <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5441</v>
+        <v>2.8951</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3444</v>
+        <v>0.1811</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3886</v>
+        <v>-0.3262</v>
       </c>
       <c r="U11" t="n">
-        <v>0.733</v>
+        <v>0.5073</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.614</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. GARCIA CARRERA</t>
+          <t>L. MAESTRO STEELE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.6534</v>
+        <v>3.2851</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2887</v>
+        <v>5.2781</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9421</v>
+        <v>-1.993</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4841</v>
+        <v>4.2698</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8961</v>
+        <v>1.3673</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.412</v>
+        <v>2.9025</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3029</v>
+        <v>6.1107</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8163</v>
+        <v>1.8215</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5134</v>
+        <v>4.2891</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1812</v>
+        <v>-1.8409</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0798</v>
+        <v>-0.4542</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1014</v>
+        <v>-1.3866</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9301</v>
+        <v>0.386</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.965</v>
+        <v>-1.158</v>
       </c>
       <c r="R12" t="n">
-        <v>2.8951</v>
+        <v>1.5441</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7608</v>
+        <v>0.4713</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6266</v>
+        <v>-0.2885</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1342</v>
+        <v>0.7598</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.614</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.4559</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. TRUEBA TAMAYO</t>
+          <t>M. CARCOBA BEDIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9742</v>
+        <v>0.7733</v>
       </c>
       <c r="E13" t="n">
-        <v>2.556</v>
+        <v>-0.3609</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5817</v>
+        <v>1.1343</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.6065</v>
+        <v>2.1655</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9729</v>
+        <v>1.8349</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.5794</v>
+        <v>0.3306</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7212</v>
+        <v>2.0245</v>
       </c>
       <c r="K13" t="n">
-        <v>1.3402</v>
+        <v>1.9353</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.619</v>
+        <v>0.0893</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3277</v>
+        <v>0.141</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.3674</v>
+        <v>-0.1003</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9604</v>
+        <v>0.2413</v>
       </c>
       <c r="P13" t="n">
-        <v>0.965</v>
+        <v>-0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.193</v>
+        <v>-2.1231</v>
       </c>
       <c r="R13" t="n">
-        <v>1.158</v>
+        <v>2.1231</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9016</v>
+        <v>0.4075</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7998</v>
+        <v>-0.2624</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1018</v>
+        <v>0.6699000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2859</v>
+        <v>-1.7997</v>
       </c>
       <c r="W13" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5138</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3563</v>
+        <v>0.5899</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2446</v>
+        <v>-0.1445</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6009</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.3974</v>
@@ -1546,13 +1546,13 @@
         <v>1.9301</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1785</v>
+        <v>0.4121</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6266</v>
+        <v>-0.5264</v>
       </c>
       <c r="U14" t="n">
-        <v>0.805</v>
+        <v>0.9386</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0266</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. CARCOBA BEDIA</t>
+          <t>D. TRUEBA TAMAYO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.5806</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5612</v>
+        <v>2.0553</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6263</v>
+        <v>-1.4746</v>
       </c>
       <c r="G15" t="n">
-        <v>2.1655</v>
+        <v>-0.6065</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8349</v>
+        <v>0.9729</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3306</v>
+        <v>-1.5794</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0245</v>
+        <v>0.7212</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9353</v>
+        <v>1.3402</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0893</v>
+        <v>-0.619</v>
       </c>
       <c r="M15" t="n">
-        <v>0.141</v>
+        <v>-1.3277</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1003</v>
+        <v>-0.3674</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2413</v>
+        <v>-0.9604</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0.965</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1231</v>
+        <v>-0.193</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3007</v>
+        <v>0.508</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4627</v>
+        <v>0.2991</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1619</v>
+        <v>0.2089</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.7997</v>
+        <v>-0.2859</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7997</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. MARTINEZ FERNANDEZ</t>
+          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.7865</v>
+        <v>-1.2808</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.029</v>
+        <v>-5.4342</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2424</v>
+        <v>4.1534</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.0927</v>
+        <v>-1.0948</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.0141</v>
+        <v>-0.0166</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9214</v>
+        <v>-1.0782</v>
       </c>
       <c r="J16" t="n">
-        <v>-2.0348</v>
+        <v>-2.8514</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.5814</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5466</v>
+        <v>-1.9871</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9421</v>
+        <v>1.7567</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5673</v>
+        <v>0.8478</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3748</v>
+        <v>0.9089</v>
       </c>
       <c r="P16" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1231</v>
+        <v>2.3161</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5461</v>
+        <v>0.2855</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3413</v>
+        <v>-0.6526999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2049</v>
+        <v>0.9382</v>
       </c>
       <c r="V16" t="n">
-        <v>-3.398</v>
+        <v>-0.8576</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.0277</v>
+        <v>-0.8576</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.678</v>
+        <v>-1.558</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7226</v>
+        <v>-1.5223</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0446</v>
+        <v>-0.0357</v>
       </c>
       <c r="G17" t="n">
         <v>-1.5504</v>
@@ -1780,13 +1780,13 @@
         <v>1.158</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3206</v>
+        <v>-0.2006</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5949</v>
+        <v>-0.3946</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2743</v>
+        <v>0.194</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. SAIZ-BUSTAMANTE GOMEZ</t>
+          <t>S. MARTINEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.4091</v>
+        <v>-2.0418</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.1352</v>
+        <v>-2.6312</v>
       </c>
       <c r="F18" t="n">
-        <v>3.7261</v>
+        <v>0.5894</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0948</v>
+        <v>-1.0927</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0166</v>
+        <v>-3.0141</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0782</v>
+        <v>1.9214</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.8514</v>
+        <v>-2.0348</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-3.5814</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9871</v>
+        <v>1.5466</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7567</v>
+        <v>0.9421</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8478</v>
+        <v>0.5673</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9089</v>
+        <v>0.3748</v>
       </c>
       <c r="P18" t="n">
-        <v>0.386</v>
+        <v>1.158</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9301</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3161</v>
+        <v>2.1231</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8428</v>
+        <v>1.2909</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3537</v>
+        <v>0.739</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5109</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.8576</v>
+        <v>-3.398</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3704</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8576</v>
+        <v>-3.0277</v>
       </c>
     </row>
     <row r="19">
@@ -1891,19 +1891,19 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>11.2666</v>
+        <v>13.2692</v>
       </c>
       <c r="E19" t="n">
-        <v>2.809000000000002</v>
+        <v>2.809000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>8.457599999999999</v>
+        <v>10.4604</v>
       </c>
       <c r="G19" t="n">
-        <v>9.3468</v>
+        <v>9.346799999999998</v>
       </c>
       <c r="H19" t="n">
-        <v>7.3118</v>
+        <v>7.311800000000001</v>
       </c>
       <c r="I19" t="n">
         <v>2.0348</v>
@@ -1915,19 +1915,19 @@
         <v>7.347100000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>5.026899999999999</v>
+        <v>5.0269</v>
       </c>
       <c r="M19" t="n">
         <v>-3.0272</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0353</v>
+        <v>-0.03529999999999989</v>
       </c>
       <c r="O19" t="n">
         <v>-2.9919</v>
       </c>
       <c r="P19" t="n">
-        <v>6.755199999999999</v>
+        <v>6.7552</v>
       </c>
       <c r="Q19" t="n">
         <v>-11.5803</v>
@@ -1936,16 +1936,16 @@
         <v>18.3357</v>
       </c>
       <c r="S19" t="n">
-        <v>2.0028</v>
+        <v>4.0055</v>
       </c>
       <c r="T19" t="n">
         <v>-2.029</v>
       </c>
       <c r="U19" t="n">
-        <v>4.0317</v>
+        <v>6.0347</v>
       </c>
       <c r="V19" t="n">
-        <v>-6.838399999999999</v>
+        <v>-6.8384</v>
       </c>
       <c r="W19" t="n">
         <v>4.0444</v>
